--- a/data/trans_dic/POLIPATOLOGIA_5-Clase-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_5-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas</t>
+          <t>Población con cinco o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,87</t>
+          <t>1,54; 4,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,25</t>
+          <t>2,26; 6,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,95</t>
+          <t>4,19; 7,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,69</t>
+          <t>2,72; 7,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 7,61</t>
+          <t>2,17; 7,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,02</t>
+          <t>2,68; 7,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,23; 11,98</t>
+          <t>7,21; 11,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,11</t>
+          <t>2,3; 5,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,43</t>
+          <t>1,11; 3,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,99</t>
+          <t>2,92; 5,9</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 9,05</t>
+          <t>6,08; 8,97</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,1</t>
+          <t>1,04; 4,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,65</t>
+          <t>0,96; 3,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,26</t>
+          <t>0,52; 3,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,19; 9,38</t>
+          <t>5,15; 9,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,43</t>
+          <t>1,98; 6,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,94</t>
+          <t>2,94; 8,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 7,29</t>
+          <t>2,26; 7,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,71; 14,98</t>
+          <t>9,61; 15,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,67</t>
+          <t>1,9; 4,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,05</t>
+          <t>2,12; 4,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,38</t>
+          <t>1,71; 4,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,88; 11,21</t>
+          <t>7,96; 11,14</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,14</t>
+          <t>2,01; 5,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,9</t>
+          <t>3,2; 7,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,33</t>
+          <t>1,47; 4,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,56; 11,65</t>
+          <t>2,53; 12,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 14,31</t>
+          <t>4,71; 13,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 9,65</t>
+          <t>3,81; 9,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,46; 21,48</t>
+          <t>9,36; 21,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,12; 25,57</t>
+          <t>15,66; 25,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 6,24</t>
+          <t>3,06; 6,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 6,98</t>
+          <t>3,95; 7,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,53</t>
+          <t>4,14; 7,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,29; 14,33</t>
+          <t>4,36; 14,16</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 5,66</t>
+          <t>3,39; 5,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,56</t>
+          <t>4,6; 7,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,04</t>
+          <t>2,73; 5,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,26; 12,73</t>
+          <t>9,19; 12,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 8,11</t>
+          <t>4,42; 7,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 8,74</t>
+          <t>4,86; 8,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 8,82</t>
+          <t>5,26; 8,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,34; 63,92</t>
+          <t>11,25; 57,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,06; 6,11</t>
+          <t>4,11; 6,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 7,57</t>
+          <t>5,1; 7,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,16; 6,21</t>
+          <t>4,19; 6,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,79; 43,52</t>
+          <t>10,88; 45,93</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,31</t>
+          <t>2,87; 6,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,76</t>
+          <t>2,23; 5,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,46</t>
+          <t>4,57; 8,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,8; 12,79</t>
+          <t>7,54; 12,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,9; 9,03</t>
+          <t>4,87; 9,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,22; 16,29</t>
+          <t>11,19; 16,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,09; 16,4</t>
+          <t>10,94; 16,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,73; 26,65</t>
+          <t>17,69; 26,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,71</t>
+          <t>4,58; 7,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,03; 11,47</t>
+          <t>8,09; 11,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,72; 12,15</t>
+          <t>8,49; 11,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,07; 20,55</t>
+          <t>14,91; 20,51</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,89</t>
+          <t>0,79; 3,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,74; 9,92</t>
+          <t>6,8; 10,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,64; 15,88</t>
+          <t>11,27; 15,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,27; 14,58</t>
+          <t>10,43; 14,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,62; 21,15</t>
+          <t>16,72; 21,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,51; 8,16</t>
+          <t>5,55; 7,95</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 12,88</t>
+          <t>9,51; 12,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,24; 11,69</t>
+          <t>8,28; 11,47</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,0; 16,66</t>
+          <t>13,08; 16,66</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,86; 4,07</t>
+          <t>2,83; 4,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,53</t>
+          <t>3,15; 4,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,13</t>
+          <t>2,93; 4,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,3; 9,03</t>
+          <t>6,17; 9,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,86; 7,68</t>
+          <t>5,94; 7,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,86; 11,01</t>
+          <t>8,75; 10,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,71; 10,85</t>
+          <t>8,87; 11,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,01; 36,14</t>
+          <t>15,91; 35,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,58; 5,67</t>
+          <t>4,6; 5,64</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,3; 7,61</t>
+          <t>6,29; 7,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,07; 7,35</t>
+          <t>6,12; 7,39</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,85; 23,0</t>
+          <t>11,83; 23,95</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas</t>
+          <t>Población con cinco o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6897; 23091</t>
+          <t>7308; 22047</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5309</t>
+          <t>0; 5953</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9382; 26821</t>
+          <t>9688; 26959</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21071; 40172</t>
+          <t>21176; 39800</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8404; 23580</t>
+          <t>8354; 24292</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7723; 23918</t>
+          <t>6823; 24334</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8602; 24351</t>
+          <t>9296; 26161</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32361; 53608</t>
+          <t>32261; 51423</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18399; 39874</t>
+          <t>17966; 39650</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8401; 25748</t>
+          <t>8345; 24443</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22546; 46473</t>
+          <t>22685; 45789</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57715; 86197</t>
+          <t>57939; 85500</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3790; 15060</t>
+          <t>3812; 16039</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3950; 15281</t>
+          <t>4026; 15593</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1918; 12288</t>
+          <t>1957; 12552</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23465; 42421</t>
+          <t>23287; 41509</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7876; 23915</t>
+          <t>7347; 23532</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9227; 26839</t>
+          <t>9934; 27055</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8783; 27126</t>
+          <t>8411; 26891</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37161; 57314</t>
+          <t>36759; 57860</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14176; 34488</t>
+          <t>14013; 32860</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16398; 38192</t>
+          <t>16033; 37180</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12584; 32804</t>
+          <t>12853; 33702</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65743; 93553</t>
+          <t>66413; 93000</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10308; 27892</t>
+          <t>10919; 27548</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19836; 43414</t>
+          <t>20127; 44111</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7553; 22614</t>
+          <t>7658; 22959</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17094; 77837</t>
+          <t>16939; 80238</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8336; 24015</t>
+          <t>7909; 23294</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9629; 25096</t>
+          <t>9912; 25828</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15712; 35691</t>
+          <t>15553; 35737</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26903; 42681</t>
+          <t>26146; 42621</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21564; 44323</t>
+          <t>21766; 44570</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35067; 62114</t>
+          <t>35179; 62807</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27354; 51825</t>
+          <t>28476; 53670</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35846; 119710</t>
+          <t>36442; 118295</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42833; 70134</t>
+          <t>41938; 71413</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53723; 87675</t>
+          <t>53260; 88194</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32375; 57993</t>
+          <t>31407; 59240</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>95787; 131742</t>
+          <t>95123; 129976</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32193; 57895</t>
+          <t>31584; 56631</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37681; 67030</t>
+          <t>37270; 66877</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43442; 72845</t>
+          <t>43446; 74208</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>110955; 625210</t>
+          <t>109988; 563018</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>79207; 119328</t>
+          <t>80183; 118845</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>98934; 145738</t>
+          <t>98265; 145199</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82128; 122662</t>
+          <t>82851; 120959</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>217270; 876078</t>
+          <t>218945; 924541</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9896; 25641</t>
+          <t>10064; 24312</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12367; 29431</t>
+          <t>11411; 28866</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28598; 52499</t>
+          <t>28387; 50565</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37072; 60764</t>
+          <t>35825; 59949</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27876; 51330</t>
+          <t>27671; 54093</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85440; 124051</t>
+          <t>85210; 125832</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81857; 121095</t>
+          <t>80727; 118488</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>140797; 224242</t>
+          <t>148838; 226428</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>41635; 70904</t>
+          <t>42114; 70756</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>102180; 145851</t>
+          <t>102874; 145752</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>118490; 165102</t>
+          <t>115334; 160354</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>198317; 270573</t>
+          <t>196257; 269943</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4587</t>
+          <t>0; 4614</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6302</t>
+          <t>0; 7826</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5700</t>
+          <t>0; 6431</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2144; 9346</t>
+          <t>1904; 8828</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>84190; 123892</t>
+          <t>84960; 125575</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>129147; 176116</t>
+          <t>125048; 174788</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>111137; 157761</t>
+          <t>112806; 157280</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>126543; 161063</t>
+          <t>127272; 161275</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>85231; 126179</t>
+          <t>85791; 122990</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>127915; 177190</t>
+          <t>130941; 176477</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>112887; 160054</t>
+          <t>113299; 157000</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>130279; 166871</t>
+          <t>131052; 166953</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>93569; 133017</t>
+          <t>92393; 134192</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>107291; 154862</t>
+          <t>107838; 156277</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>98930; 139955</t>
+          <t>99332; 141149</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>212693; 305014</t>
+          <t>208211; 307055</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>198097; 259381</t>
+          <t>200553; 260632</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>314422; 390724</t>
+          <t>310719; 388443</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>307526; 383064</t>
+          <t>313142; 391427</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>572794; 1293143</t>
+          <t>569078; 1282674</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>304440; 376632</t>
+          <t>305809; 374674</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>439088; 530547</t>
+          <t>438876; 525988</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>419782; 508126</t>
+          <t>423128; 511200</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>824372; 1599441</t>
+          <t>822691; 1665216</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_5-Clase-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_5-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,65</t>
+          <t>1,42; 4,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,28</t>
+          <t>2,17; 6,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,88</t>
+          <t>4,5; 8,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,92</t>
+          <t>2,46; 7,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,74</t>
+          <t>2,21; 7,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,54</t>
+          <t>2,52; 7,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,21; 11,49</t>
+          <t>7,27; 11,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,08</t>
+          <t>2,45; 5,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,25</t>
+          <t>1,07; 3,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,9</t>
+          <t>2,95; 6,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,08; 8,97</t>
+          <t>6,29; 9,14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,37</t>
+          <t>1,19; 4,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,72</t>
+          <t>0,95; 3,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,33</t>
+          <t>0,51; 3,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,15; 9,18</t>
+          <t>5,12; 9,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,33</t>
+          <t>2,07; 6,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,0</t>
+          <t>2,96; 7,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,22</t>
+          <t>2,26; 7,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,61; 15,12</t>
+          <t>10,04; 15,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,45</t>
+          <t>1,98; 4,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,91</t>
+          <t>2,05; 4,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,5</t>
+          <t>1,71; 4,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,96; 11,14</t>
+          <t>7,86; 11,35</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,08</t>
+          <t>1,88; 4,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,01</t>
+          <t>3,22; 6,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,4</t>
+          <t>1,52; 4,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 12,01</t>
+          <t>8,19; 13,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,71; 13,88</t>
+          <t>4,87; 14,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 9,93</t>
+          <t>3,69; 10,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,36; 21,51</t>
+          <t>9,37; 21,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,66; 25,54</t>
+          <t>15,57; 24,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,28</t>
+          <t>3,16; 6,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,95; 7,06</t>
+          <t>3,88; 7,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,8</t>
+          <t>3,85; 7,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 14,16</t>
+          <t>11,03; 15,72</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,77</t>
+          <t>3,42; 5,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,61</t>
+          <t>4,82; 7,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,15</t>
+          <t>2,83; 5,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,19; 12,56</t>
+          <t>8,89; 12,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 7,93</t>
+          <t>4,41; 7,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 8,72</t>
+          <t>5,11; 8,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 8,99</t>
+          <t>5,34; 8,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,25; 57,56</t>
+          <t>10,27; 13,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,09</t>
+          <t>4,08; 6,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,1; 7,54</t>
+          <t>5,15; 7,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,19; 6,12</t>
+          <t>4,07; 6,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,88; 45,93</t>
+          <t>9,88; 12,38</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,94</t>
+          <t>2,93; 7,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,65</t>
+          <t>2,32; 5,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 8,15</t>
+          <t>4,59; 8,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 12,62</t>
+          <t>6,77; 11,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,87; 9,51</t>
+          <t>4,67; 9,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,19; 16,52</t>
+          <t>11,37; 16,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,94; 16,05</t>
+          <t>10,73; 15,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,69; 26,91</t>
+          <t>22,69; 27,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,7</t>
+          <t>4,54; 7,57</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,09; 11,46</t>
+          <t>8,12; 11,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,49; 11,8</t>
+          <t>8,56; 11,81</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,91; 20,51</t>
+          <t>16,81; 20,16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,67</t>
+          <t>1,09; 5,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,8; 10,06</t>
+          <t>6,63; 9,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,27; 15,76</t>
+          <t>11,56; 15,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,43; 14,54</t>
+          <t>10,43; 14,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,72; 21,18</t>
+          <t>16,37; 20,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,95</t>
+          <t>5,59; 8,0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,51; 12,82</t>
+          <t>9,29; 12,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,28; 11,47</t>
+          <t>8,31; 11,81</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,08; 16,66</t>
+          <t>13,08; 16,87</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,1</t>
+          <t>2,84; 4,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,57</t>
+          <t>3,12; 4,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,17</t>
+          <t>2,98; 4,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,1</t>
+          <t>7,54; 9,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,94; 7,72</t>
+          <t>5,88; 7,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,75; 10,94</t>
+          <t>8,89; 10,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,87; 11,08</t>
+          <t>8,74; 10,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,91; 35,85</t>
+          <t>15,49; 17,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,6; 5,64</t>
+          <t>4,58; 5,62</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,29; 7,54</t>
+          <t>6,23; 7,5</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,12; 7,39</t>
+          <t>6,1; 7,35</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,83; 23,95</t>
+          <t>11,88; 13,24</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29797</t>
+          <t>33130</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40979</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70777</t>
+          <t>78112</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7308; 22047</t>
+          <t>6743; 21931</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5953</t>
+          <t>0; 5260</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9688; 26959</t>
+          <t>9290; 26893</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21176; 39800</t>
+          <t>24760; 44996</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8354; 24292</t>
+          <t>7544; 23330</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6823; 24334</t>
+          <t>6940; 22782</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9296; 26161</t>
+          <t>8737; 25954</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32261; 51423</t>
+          <t>35508; 57661</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17966; 39650</t>
+          <t>19098; 39747</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8345; 24443</t>
+          <t>8065; 24548</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22685; 45789</t>
+          <t>22892; 47099</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57939; 85500</t>
+          <t>65324; 95002</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31840</t>
+          <t>33639</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>46721</t>
+          <t>51854</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78562</t>
+          <t>85494</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3812; 16039</t>
+          <t>4369; 15968</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4026; 15593</t>
+          <t>3977; 15837</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1957; 12552</t>
+          <t>1933; 12289</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23287; 41509</t>
+          <t>24764; 44528</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7347; 23532</t>
+          <t>7686; 23337</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9934; 27055</t>
+          <t>10009; 26560</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8411; 26891</t>
+          <t>8400; 26849</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36759; 57860</t>
+          <t>42504; 64116</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14013; 32860</t>
+          <t>14622; 33497</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16033; 37180</t>
+          <t>15497; 36365</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12853; 33702</t>
+          <t>12838; 33547</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>66413; 93000</t>
+          <t>71281; 102879</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46210</t>
+          <t>50209</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33998</t>
+          <t>37446</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80208</t>
+          <t>87656</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10919; 27548</t>
+          <t>10185; 27006</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20127; 44111</t>
+          <t>20277; 43819</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7658; 22959</t>
+          <t>7922; 23437</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16939; 80238</t>
+          <t>38626; 63177</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7909; 23294</t>
+          <t>8177; 23984</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9912; 25828</t>
+          <t>9604; 26138</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15553; 35737</t>
+          <t>15568; 35239</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26146; 42621</t>
+          <t>29196; 46531</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21766; 44570</t>
+          <t>22419; 44252</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35179; 62807</t>
+          <t>34559; 62706</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28476; 53670</t>
+          <t>26480; 53040</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36442; 118295</t>
+          <t>72714; 103642</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111030</t>
+          <t>117379</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>297180</t>
+          <t>102740</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>408209</t>
+          <t>220119</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41938; 71413</t>
+          <t>42346; 70930</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53260; 88194</t>
+          <t>55874; 91346</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31407; 59240</t>
+          <t>32495; 58382</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>95123; 129976</t>
+          <t>100642; 137538</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31584; 56631</t>
+          <t>31469; 56453</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37270; 66877</t>
+          <t>39154; 68826</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43446; 74208</t>
+          <t>44070; 71908</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>109988; 563018</t>
+          <t>88421; 119262</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>80183; 118845</t>
+          <t>79592; 117581</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>98265; 145199</t>
+          <t>99161; 144118</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82851; 120959</t>
+          <t>80311; 120662</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>218945; 924541</t>
+          <t>196949; 246640</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47005</t>
+          <t>49579</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>193991</t>
+          <t>207250</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>240996</t>
+          <t>256830</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10064; 24312</t>
+          <t>10261; 25004</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11411; 28866</t>
+          <t>11825; 29167</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28387; 50565</t>
+          <t>28472; 51601</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35825; 59949</t>
+          <t>38430; 62930</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27671; 54093</t>
+          <t>26559; 52157</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85210; 125832</t>
+          <t>86595; 122623</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80727; 118488</t>
+          <t>79181; 118041</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>148838; 226428</t>
+          <t>188520; 227515</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42114; 70756</t>
+          <t>41727; 69569</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>102874; 145752</t>
+          <t>103324; 146769</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>115334; 160354</t>
+          <t>116321; 160536</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>196257; 269943</t>
+          <t>235158; 282056</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>143271</t>
+          <t>154761</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>147680</t>
+          <t>160765</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4614</t>
+          <t>0; 4599</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 7826</t>
+          <t>0; 6055</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6431</t>
+          <t>0; 5693</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1904; 8828</t>
+          <t>2584; 12552</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>84960; 125575</t>
+          <t>82777; 122908</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>125048; 174788</t>
+          <t>128191; 175363</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>112806; 157280</t>
+          <t>112821; 156791</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>127272; 161275</t>
+          <t>138203; 173710</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>85791; 122990</t>
+          <t>86499; 123787</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>130941; 176477</t>
+          <t>127897; 174852</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>113299; 157000</t>
+          <t>113794; 161748</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>131052; 166953</t>
+          <t>141410; 182493</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>270291</t>
+          <t>289942</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>756140</t>
+          <t>599033</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1026432</t>
+          <t>888975</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>92393; 134192</t>
+          <t>92989; 133511</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>107838; 156277</t>
+          <t>106850; 154509</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>99332; 141149</t>
+          <t>100731; 143874</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>208211; 307055</t>
+          <t>259501; 321721</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>200553; 260632</t>
+          <t>198795; 256965</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>310719; 388443</t>
+          <t>315548; 388454</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>313142; 391427</t>
+          <t>308726; 386353</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>569078; 1282674</t>
+          <t>563125; 635478</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>305809; 374674</t>
+          <t>304714; 373814</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>438876; 525988</t>
+          <t>434181; 522665</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>423128; 511200</t>
+          <t>422214; 508456</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>822691; 1665216</t>
+          <t>840966; 937122</t>
         </is>
       </c>
     </row>
